--- a/reports/pdf_rolling5_20261006.xlsx
+++ b/reports/pdf_rolling5_20261006.xlsx
@@ -59,13 +59,13 @@
       <color rgb="000070C0"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="8">
@@ -171,11 +171,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-09-28 ~ 2026-10-06  (최근 5거래일)  ·  캡처 4/7  ·  대기: TIME, TIME, RISE</t>
+          <t>최근 5거래일 변화  ·  2026-09-28 ~ 2026-10-06  (최근 5거래일)  ·  캡처 6/7  ·  대기: RISE</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,330억   ·   현금 19억(0.4%)      오늘 2026-10-06  vs  5일전 2026-09-28      매수 10종목  /  매도 7종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,330억   ·   현금 9억(0.2%)      오늘 2026-10-06  vs  5일전 2026-09-28      매수 10종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1055,7 +1055,7 @@
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,475억   ·   현금 44억(1.3%)      오늘 2026-10-06  vs  5일전 2026-09-28      매수 7종목  /  매도 5종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,475억   ·   현금 22억(0.6%)      오늘 2026-10-06  vs  5일전 2026-09-28      매수 7종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -1364,23 +1364,23 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>녹십자</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>954998000</v>
+        <v>657934000</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>8.24%→8.41%</t>
+          <t>3.57%→3.68%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>286→296</t>
+          <t>178→188</t>
         </is>
       </c>
       <c r="G25" s="17" t="n"/>
@@ -1392,23 +1392,23 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>녹십자</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>657934000</v>
+        <v>954998000</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>3.57%→3.68%</t>
+          <t>8.24%→8.41%</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>178→188</t>
+          <t>286→296</t>
         </is>
       </c>
       <c r="G26" s="17" t="n"/>
@@ -1418,479 +1418,765 @@
       <c r="K26" s="17" t="n"/>
     </row>
     <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="n"/>
-      <c r="C28" s="19" t="n"/>
-      <c r="D28" s="19" t="n"/>
-      <c r="E28" s="19" t="n"/>
-      <c r="F28" s="19" t="n"/>
-      <c r="G28" s="19" t="n"/>
-      <c r="H28" s="19" t="n"/>
-      <c r="I28" s="19" t="n"/>
-      <c r="J28" s="19" t="n"/>
-      <c r="K28" s="19" t="n"/>
-    </row>
-    <row r="30" ht="19" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="n"/>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="19" t="n"/>
-      <c r="E30" s="19" t="n"/>
-      <c r="F30" s="19" t="n"/>
-      <c r="G30" s="19" t="n"/>
-      <c r="H30" s="19" t="n"/>
-      <c r="I30" s="19" t="n"/>
-      <c r="J30" s="19" t="n"/>
-      <c r="K30" s="19" t="n"/>
-    </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 326억   ·   현금 3억(1.0%)      오늘 2026-10-06  vs  5일전 2026-09-28      매수 6종목  /  매도 7종목</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
-      <c r="J32" s="4" t="n"/>
-      <c r="K32" s="4" t="n"/>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,868억   ·   현금 84억(2.9%)      오늘 2026-10-06  vs  5일전 2026-09-28      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="19" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,140억   ·   현금 17억(0.8%)      오늘 2026-10-06  vs  5일전 2026-09-28      매수 4종목  /  매도 5종목</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="8" t="n"/>
+      <c r="J32" s="8" t="n"/>
+      <c r="K32" s="8" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="n"/>
-      <c r="J33" s="8" t="n"/>
-      <c r="K33" s="8" t="n"/>
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H34" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J34" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K34" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>지투지바이오</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n">
+        <v>456</v>
+      </c>
+      <c r="C34" s="11" t="n">
+        <v>7177256009</v>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>2.33%→6.43%</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>396→852</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>셀트리온제약  (편출)</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>-205</v>
+      </c>
+      <c r="I34" s="15" t="n">
+        <v>-2889894610</v>
+      </c>
+      <c r="J34" s="16" t="inlineStr">
+        <is>
+          <t>1.47%→0.00%</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>205→0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>더블유씨피</t>
+          <t>인벤티지랩</t>
         </is>
       </c>
       <c r="B35" s="11" t="n">
-        <v>111</v>
+        <v>279</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>80885700</v>
+        <v>2850347068</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>6.81%→7.07%</t>
+          <t>1.24%→2.72%</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>3,034→3,145</t>
+          <t>276→555</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
-        <v>-68</v>
+        <v>-60</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-191590000</v>
+        <v>-2020877552</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>7.93%→7.35%</t>
+          <t>4.18%→3.05%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>913→845</t>
+          <t>249→189</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B36" s="11" t="n">
-        <v>44</v>
+        <v>221</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>67298000</v>
+        <v>2301681340</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>2.09%→2.30%</t>
+          <t>2.09%→3.43%</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>443→487</t>
+          <t>465→686</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>에프앤가이드</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-33</v>
+        <v>-45</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-48741000</v>
+        <v>-834992815</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>3.85%→3.70%</t>
+          <t>3.99%→3.40%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>845→812</t>
+          <t>427→382</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="C37" s="11" t="n">
+        <v>2043476147</v>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>10.96%→11.60%</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>336→367</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>한미약품</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="n">
+        <v>-27</v>
+      </c>
+      <c r="I37" s="15" t="n">
+        <v>-4931980907</v>
+      </c>
+      <c r="J37" s="16" t="inlineStr">
+        <is>
+          <t>11.56%→8.24%</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="inlineStr">
+        <is>
+          <t>121→94</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="n"/>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>보로노이</t>
+        </is>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I38" s="15" t="n">
+        <v>-624241062</v>
+      </c>
+      <c r="J38" s="16" t="inlineStr">
+        <is>
+          <t>5.06%→4.37%</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>187→175</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="19" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 326억   ·   현금 27억(7.6%)      오늘 2026-10-06  vs  5일전 2026-09-28      매수 6종목  /  매도 7종목</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="4" t="n"/>
+      <c r="K40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="n"/>
+      <c r="I41" s="8" t="n"/>
+      <c r="J41" s="8" t="n"/>
+      <c r="K41" s="8" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K42" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>더블유씨피</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="n">
+        <v>111</v>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>83993700</v>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>7.07%→7.34%</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>3,034→3,145</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="H43" s="15" t="n">
+        <v>-68</v>
+      </c>
+      <c r="I43" s="15" t="n">
+        <v>-197540000</v>
+      </c>
+      <c r="J43" s="16" t="inlineStr">
+        <is>
+          <t>8.17%→7.57%</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="inlineStr">
+        <is>
+          <t>913→845</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>68684000</v>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>2.13%→2.34%</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>443→487</t>
+        </is>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>에프앤가이드</t>
+        </is>
+      </c>
+      <c r="H44" s="15" t="n">
+        <v>-33</v>
+      </c>
+      <c r="I44" s="15" t="n">
+        <v>-48625500</v>
+      </c>
+      <c r="J44" s="16" t="inlineStr">
+        <is>
+          <t>3.84%→3.69%</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="inlineStr">
+        <is>
+          <t>845→812</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
           <t>씨어스</t>
         </is>
       </c>
-      <c r="B37" s="11" t="n">
+      <c r="B45" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="C37" s="11" t="n">
-        <v>63822500</v>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>4.68%→4.88%</t>
-        </is>
-      </c>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="C45" s="11" t="n">
+        <v>66150000</v>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>4.85%→5.06%</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
         <is>
           <t>833→868</t>
         </is>
       </c>
-      <c r="G37" s="14" t="inlineStr">
+      <c r="G45" s="14" t="inlineStr">
         <is>
           <t>원익머트리얼즈</t>
         </is>
       </c>
-      <c r="H37" s="15" t="n">
+      <c r="H45" s="15" t="n">
         <v>-14</v>
       </c>
-      <c r="I37" s="15" t="n">
-        <v>-41160000</v>
-      </c>
-      <c r="J37" s="16" t="inlineStr">
-        <is>
-          <t>2.26%→2.13%</t>
-        </is>
-      </c>
-      <c r="K37" s="13" t="inlineStr">
+      <c r="I45" s="15" t="n">
+        <v>-40376000</v>
+      </c>
+      <c r="J45" s="16" t="inlineStr">
+        <is>
+          <t>2.21%→2.09%</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="inlineStr">
         <is>
           <t>249→235</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>인텍플러스</t>
         </is>
       </c>
-      <c r="B38" s="11" t="n">
+      <c r="B46" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="C38" s="11" t="n">
-        <v>81200000</v>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>3.74%→4.00%</t>
-        </is>
-      </c>
-      <c r="E38" s="13" t="inlineStr">
+      <c r="C46" s="11" t="n">
+        <v>82740000</v>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>3.81%→4.07%</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
         <is>
           <t>299→319</t>
         </is>
       </c>
-      <c r="G38" s="14" t="inlineStr">
+      <c r="G46" s="14" t="inlineStr">
         <is>
           <t>새로닉스</t>
         </is>
       </c>
-      <c r="H38" s="15" t="n">
+      <c r="H46" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="I38" s="15" t="n">
-        <v>-7654500</v>
-      </c>
-      <c r="J38" s="16" t="inlineStr">
-        <is>
-          <t>2.06%→2.04%</t>
-        </is>
-      </c>
-      <c r="K38" s="13" t="inlineStr">
+      <c r="I46" s="15" t="n">
+        <v>-7018200</v>
+      </c>
+      <c r="J46" s="16" t="inlineStr">
+        <is>
+          <t>1.89%→1.87%</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
         <is>
           <t>786→777</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>한중엔시에스</t>
         </is>
       </c>
-      <c r="B39" s="11" t="n">
+      <c r="B47" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="C39" s="11" t="n">
-        <v>58380000</v>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>2.14%→2.32%</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="inlineStr">
+      <c r="C47" s="11" t="n">
+        <v>59080000</v>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>2.17%→2.35%</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
         <is>
           <t>238→258</t>
         </is>
       </c>
-      <c r="G39" s="14" t="inlineStr">
+      <c r="G47" s="14" t="inlineStr">
         <is>
           <t>브이엠</t>
         </is>
       </c>
-      <c r="H39" s="15" t="n">
+      <c r="H47" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I39" s="15" t="n">
-        <v>-34692000</v>
-      </c>
-      <c r="J39" s="16" t="inlineStr">
-        <is>
-          <t>3.06%→2.95%</t>
-        </is>
-      </c>
-      <c r="K39" s="13" t="inlineStr">
+      <c r="I47" s="15" t="n">
+        <v>-32389000</v>
+      </c>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>2.85%→2.75%</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
         <is>
           <t>200→193</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>실리콘투</t>
         </is>
       </c>
-      <c r="B40" s="11" t="n">
+      <c r="B48" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="C40" s="11" t="n">
-        <v>40215000</v>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>1.05%→1.17%</t>
-        </is>
-      </c>
-      <c r="E40" s="13" t="inlineStr">
+      <c r="C48" s="11" t="n">
+        <v>38955000</v>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>1.02%→1.14%</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
         <is>
           <t>127→142</t>
         </is>
       </c>
-      <c r="G40" s="14" t="inlineStr">
+      <c r="G48" s="14" t="inlineStr">
         <is>
           <t>테스</t>
         </is>
       </c>
-      <c r="H40" s="15" t="n">
+      <c r="H48" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I40" s="15" t="n">
-        <v>-77238000</v>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>3.09%→2.86%</t>
-        </is>
-      </c>
-      <c r="K40" s="13" t="inlineStr">
+      <c r="I48" s="15" t="n">
+        <v>-74508000</v>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>2.98%→2.76%</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
         <is>
           <t>78→72</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="17" t="n"/>
-      <c r="B41" s="17" t="n"/>
-      <c r="C41" s="17" t="n"/>
-      <c r="D41" s="17" t="n"/>
-      <c r="E41" s="17" t="n"/>
-      <c r="G41" s="14" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="17" t="n"/>
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="G49" s="14" t="inlineStr">
         <is>
           <t>비나텍</t>
         </is>
       </c>
-      <c r="H41" s="15" t="n">
+      <c r="H49" s="15" t="n">
         <v>-5</v>
       </c>
-      <c r="I41" s="15" t="n">
-        <v>-32795000</v>
-      </c>
-      <c r="J41" s="16" t="inlineStr">
-        <is>
-          <t>1.31%→1.21%</t>
-        </is>
-      </c>
-      <c r="K41" s="13" t="inlineStr">
+      <c r="I49" s="15" t="n">
+        <v>-33180000</v>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>1.33%→1.23%</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
         <is>
           <t>65→60</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="19" customHeight="1">
-      <c r="A43" s="18" t="inlineStr">
+    <row r="51" ht="19" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B43" s="19" t="n"/>
-      <c r="C43" s="19" t="n"/>
-      <c r="D43" s="19" t="n"/>
-      <c r="E43" s="19" t="n"/>
-      <c r="F43" s="19" t="n"/>
-      <c r="G43" s="19" t="n"/>
-      <c r="H43" s="19" t="n"/>
-      <c r="I43" s="19" t="n"/>
-      <c r="J43" s="19" t="n"/>
-      <c r="K43" s="19" t="n"/>
-    </row>
-    <row r="45" ht="19" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="B51" s="20" t="n"/>
+      <c r="C51" s="20" t="n"/>
+      <c r="D51" s="20" t="n"/>
+      <c r="E51" s="20" t="n"/>
+      <c r="F51" s="20" t="n"/>
+      <c r="G51" s="20" t="n"/>
+      <c r="H51" s="20" t="n"/>
+      <c r="I51" s="20" t="n"/>
+      <c r="J51" s="20" t="n"/>
+      <c r="K51" s="20" t="n"/>
+    </row>
+    <row r="53" ht="19" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,210억      오늘 2026-10-06  vs  5일전 2026-09-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B45" s="4" t="n"/>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="n"/>
-      <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="n"/>
-      <c r="J45" s="4" t="n"/>
-      <c r="K45" s="4" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="20" t="inlineStr">
+      <c r="B53" s="4" t="n"/>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="n"/>
+      <c r="G53" s="4" t="n"/>
+      <c r="H53" s="4" t="n"/>
+      <c r="I53" s="4" t="n"/>
+      <c r="J53" s="4" t="n"/>
+      <c r="K53" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="19">
+    <mergeCell ref="A51:K51"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A54:K54"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="G18:K18"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A53:K53"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A30:K30"/>
-    <mergeCell ref="A43:K43"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="G33:K33"/>
-    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="G32:K32"/>
+    <mergeCell ref="G41:K41"/>
     <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A46:K46"/>
-    <mergeCell ref="A32:K32"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A17:K17"/>
-    <mergeCell ref="G18:K18"/>
-    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20261006.xlsx
+++ b/reports/pdf_rolling5_20261006.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,330억   ·   현금 9억(0.2%)      오늘 2026-10-06  vs  5일전 2026-09-28      매수 10종목  /  매도 7종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,293억   ·   현금 9억(0.2%)      오늘 2026-10-06  vs  5일전 2026-09-28      매수 10종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>61</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1187742932</v>
+        <v>1186526785</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-199</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-6613325709</v>
+        <v>-6606554231</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>58</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>3034188116</v>
+        <v>3031081368</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-69</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1969811556</v>
+        <v>-1967794638</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>40</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>3291071258</v>
+        <v>3287701484</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-28</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1407391683</v>
+        <v>-1405950634</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>26</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>525283082</v>
+        <v>524745237</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-21</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-772699026</v>
+        <v>-771907848</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2012121146</v>
+        <v>2010060907</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-14</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-731023835</v>
+        <v>-730275330</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>20</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>810079817</v>
+        <v>809250365</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-8</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-317395128</v>
+        <v>-317070143</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>18</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1045295764</v>
+        <v>1044225471</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-5</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1266359715</v>
+        <v>-1265063071</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>13</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>215949711</v>
+        <v>215728597</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>5</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>236435947</v>
+        <v>236193857</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>866687805</v>
+        <v>865800391</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,475억   ·   현금 22억(0.6%)      오늘 2026-10-06  vs  5일전 2026-09-28      매수 7종목  /  매도 5종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,381억   ·   현금 22억(0.6%)      오늘 2026-10-06  vs  5일전 2026-09-28      매수 7종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -1151,7 +1151,7 @@
         <v>130</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>2964364000</v>
+        <v>2964364907</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>-385</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-1558487700</v>
+        <v>-1558488177</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>119</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1795537450</v>
+        <v>1795537999</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>-243</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-2070279810</v>
+        <v>-2070280443</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>86</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>2311869200</v>
+        <v>2311869907</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>-70</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-917080500</v>
+        <v>-917080781</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>50</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>729585000</v>
+        <v>729585223</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>-20</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-975918000</v>
+        <v>-975918299</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>43</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>1036742900</v>
+        <v>1036743217</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>-19</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-315499750</v>
+        <v>-315499847</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1364,23 +1364,23 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>녹십자</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>657934000</v>
+        <v>954998292</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>3.57%→3.68%</t>
+          <t>8.24%→8.41%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>178→188</t>
+          <t>286→296</t>
         </is>
       </c>
       <c r="G25" s="17" t="n"/>
@@ -1392,23 +1392,23 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>녹십자</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>954998000</v>
+        <v>657934201</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>8.24%→8.41%</t>
+          <t>3.57%→3.68%</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>286→296</t>
+          <t>178→188</t>
         </is>
       </c>
       <c r="G26" s="17" t="n"/>
@@ -1420,7 +1420,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,868억   ·   현금 84억(2.9%)      오늘 2026-10-06  vs  5일전 2026-09-28      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,842억   ·   현금 42억(1.5%)      오늘 2026-10-06  vs  5일전 2026-09-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1444,7 +1444,7 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,140억   ·   현금 17억(0.8%)      오늘 2026-10-06  vs  5일전 2026-09-28      매수 4종목  /  매도 5종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,093억   ·   현금 9억(0.4%)      오늘 2026-10-06  vs  5일전 2026-09-28      매수 4종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1540,7 +1540,7 @@
         <v>456</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>7177256009</v>
+        <v>7177260781</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>-205</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-2889894610</v>
+        <v>-2889896531</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>279</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>2850347068</v>
+        <v>2850348963</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>-60</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-2020877552</v>
+        <v>-2020878896</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>221</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>2301681340</v>
+        <v>2301682870</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>-45</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-834992815</v>
+        <v>-834993370</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>31</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>2043476147</v>
+        <v>2043477506</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>-27</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-4931980907</v>
+        <v>-4931984186</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>-12</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-624241062</v>
+        <v>-624241477</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 326억   ·   현금 27억(7.6%)      오늘 2026-10-06  vs  5일전 2026-09-28      매수 6종목  /  매도 7종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 316억   ·   현금 3억(1.0%)      오늘 2026-10-06  vs  5일전 2026-09-28      매수 6종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B40" s="4" t="n"/>
@@ -1833,7 +1833,7 @@
         <v>111</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>83993700</v>
+        <v>81593856</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>-68</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-197540000</v>
+        <v>-191895944</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>44</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>68684000</v>
+        <v>66721580</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>-33</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-48625500</v>
+        <v>-47236186</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>35</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>66150000</v>
+        <v>64259981</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>-14</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-40376000</v>
+        <v>-39222388</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
@@ -1958,23 +1958,23 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>82740000</v>
+        <v>57391983</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>3.81%→4.07%</t>
+          <t>2.17%→2.35%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>299→319</t>
+          <t>238→258</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -1986,7 +1986,7 @@
         <v>-9</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-7018200</v>
+        <v>-6817678</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
@@ -2002,23 +2002,23 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>59080000</v>
+        <v>80375976</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>2.17%→2.35%</t>
+          <t>3.81%→4.07%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>238→258</t>
+          <t>299→319</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
@@ -2030,7 +2030,7 @@
         <v>-7</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-32389000</v>
+        <v>-31463591</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>15</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>38955000</v>
+        <v>37841989</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>-6</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-74508000</v>
+        <v>-72379179</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>-5</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-33180000</v>
+        <v>-32231991</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
     <row r="53" ht="19" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,210억      오늘 2026-10-06  vs  5일전 2026-09-28      매수 0종목  /  매도 0종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,175억      오늘 2026-10-06  vs  5일전 2026-09-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B53" s="4" t="n"/>

--- a/reports/pdf_rolling5_20261006.xlsx
+++ b/reports/pdf_rolling5_20261006.xlsx
@@ -1364,23 +1364,23 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>녹십자</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>954998292</v>
+        <v>657934201</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>8.24%→8.41%</t>
+          <t>3.57%→3.68%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>286→296</t>
+          <t>178→188</t>
         </is>
       </c>
       <c r="G25" s="17" t="n"/>
@@ -1392,23 +1392,23 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>녹십자</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>657934201</v>
+        <v>954998292</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>3.57%→3.68%</t>
+          <t>8.24%→8.41%</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>178→188</t>
+          <t>286→296</t>
         </is>
       </c>
       <c r="G26" s="17" t="n"/>
@@ -1958,23 +1958,23 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>57391983</v>
+        <v>80375976</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>2.17%→2.35%</t>
+          <t>3.81%→4.07%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>238→258</t>
+          <t>299→319</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -2002,23 +2002,23 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>80375976</v>
+        <v>57391983</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>3.81%→4.07%</t>
+          <t>2.17%→2.35%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>299→319</t>
+          <t>238→258</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20261006.xlsx
+++ b/reports/pdf_rolling5_20261006.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1737,7 +1737,7 @@
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 316억   ·   현금 3억(1.0%)      오늘 2026-10-06  vs  5일전 2026-09-28      매수 6종목  /  매도 7종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 316억   ·   현금 4억(1.2%)      오늘 2026-10-06  vs  5일전 2026-09-28      매수 7종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B40" s="4" t="n"/>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>7.07%→7.34%</t>
+          <t>7.07%→7.35%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -1847,23 +1847,23 @@
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>새로닉스</t>
         </is>
       </c>
       <c r="H43" s="15" t="n">
-        <v>-68</v>
+        <v>-118</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-191895944</v>
+        <v>-89387334</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>8.17%→7.57%</t>
+          <t>1.89%→1.61%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>913→845</t>
+          <t>786→668</t>
         </is>
       </c>
     </row>
@@ -1874,40 +1874,40 @@
         </is>
       </c>
       <c r="B44" s="11" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>66721580</v>
+        <v>87951174</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>2.13%→2.34%</t>
+          <t>2.13%→2.42%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>443→487</t>
+          <t>443→501</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>에프앤가이드</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
-        <v>-33</v>
+        <v>-68</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-47236186</v>
+        <v>-191895944</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>3.84%→3.69%</t>
+          <t>8.17%→7.58%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>845→812</t>
+          <t>913→845</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>4.85%→5.06%</t>
+          <t>4.85%→5.07%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -1935,67 +1935,67 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>에프앤가이드</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
-        <v>-14</v>
+        <v>-33</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-39222388</v>
+        <v>-47236186</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>2.21%→2.09%</t>
+          <t>3.84%→3.70%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>249→235</t>
+          <t>845→812</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>필옵틱스  (신규)</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>80375976</v>
+        <v>94676372</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>3.81%→4.07%</t>
+          <t>0.00%→0.30%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>299→319</t>
+          <t>0→34</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>새로닉스</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-9</v>
+        <v>-14</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-6817678</v>
+        <v>-39222388</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>1.89%→1.87%</t>
+          <t>2.21%→2.09%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>786→777</t>
+          <t>249→235</t>
         </is>
       </c>
     </row>
@@ -2023,134 +2023,178 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-31463591</v>
+        <v>-108568768</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>2.85%→2.75%</t>
+          <t>2.98%→2.65%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>200→193</t>
+          <t>78→69</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>80375976</v>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>3.81%→4.08%</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>299→319</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I48" s="15" t="n">
+        <v>-31463591</v>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>2.85%→2.76%</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>200→193</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
           <t>실리콘투</t>
         </is>
       </c>
-      <c r="B48" s="11" t="n">
+      <c r="B49" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="C48" s="11" t="n">
+      <c r="C49" s="11" t="n">
         <v>37841989</v>
       </c>
-      <c r="D48" s="12" t="inlineStr">
+      <c r="D49" s="12" t="inlineStr">
         <is>
           <t>1.02%→1.14%</t>
         </is>
       </c>
-      <c r="E48" s="13" t="inlineStr">
+      <c r="E49" s="13" t="inlineStr">
         <is>
           <t>127→142</t>
         </is>
       </c>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>테스</t>
-        </is>
-      </c>
-      <c r="H48" s="15" t="n">
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>두산테스나</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I48" s="15" t="n">
-        <v>-72379179</v>
-      </c>
-      <c r="J48" s="16" t="inlineStr">
-        <is>
-          <t>2.98%→2.76%</t>
-        </is>
-      </c>
-      <c r="K48" s="13" t="inlineStr">
-        <is>
-          <t>78→72</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="17" t="n"/>
-      <c r="B49" s="17" t="n"/>
-      <c r="C49" s="17" t="n"/>
-      <c r="D49" s="17" t="n"/>
-      <c r="E49" s="17" t="n"/>
-      <c r="G49" s="14" t="inlineStr">
+      <c r="I49" s="15" t="n">
+        <v>-43615187</v>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>2.21%→2.08%</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>96→90</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="n"/>
+      <c r="B50" s="17" t="n"/>
+      <c r="C50" s="17" t="n"/>
+      <c r="D50" s="17" t="n"/>
+      <c r="E50" s="17" t="n"/>
+      <c r="G50" s="14" t="inlineStr">
         <is>
           <t>비나텍</t>
         </is>
       </c>
-      <c r="H49" s="15" t="n">
+      <c r="H50" s="15" t="n">
         <v>-5</v>
       </c>
-      <c r="I49" s="15" t="n">
+      <c r="I50" s="15" t="n">
         <v>-32231991</v>
       </c>
-      <c r="J49" s="16" t="inlineStr">
+      <c r="J50" s="16" t="inlineStr">
         <is>
           <t>1.33%→1.23%</t>
         </is>
       </c>
-      <c r="K49" s="13" t="inlineStr">
+      <c r="K50" s="13" t="inlineStr">
         <is>
           <t>65→60</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="19" customHeight="1">
-      <c r="A51" s="19" t="inlineStr">
+    <row r="52" ht="19" customHeight="1">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B51" s="20" t="n"/>
-      <c r="C51" s="20" t="n"/>
-      <c r="D51" s="20" t="n"/>
-      <c r="E51" s="20" t="n"/>
-      <c r="F51" s="20" t="n"/>
-      <c r="G51" s="20" t="n"/>
-      <c r="H51" s="20" t="n"/>
-      <c r="I51" s="20" t="n"/>
-      <c r="J51" s="20" t="n"/>
-      <c r="K51" s="20" t="n"/>
-    </row>
-    <row r="53" ht="19" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="B52" s="20" t="n"/>
+      <c r="C52" s="20" t="n"/>
+      <c r="D52" s="20" t="n"/>
+      <c r="E52" s="20" t="n"/>
+      <c r="F52" s="20" t="n"/>
+      <c r="G52" s="20" t="n"/>
+      <c r="H52" s="20" t="n"/>
+      <c r="I52" s="20" t="n"/>
+      <c r="J52" s="20" t="n"/>
+      <c r="K52" s="20" t="n"/>
+    </row>
+    <row r="54" ht="19" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,175억      오늘 2026-10-06  vs  5일전 2026-09-28      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B53" s="4" t="n"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-      <c r="F53" s="4" t="n"/>
-      <c r="G53" s="4" t="n"/>
-      <c r="H53" s="4" t="n"/>
-      <c r="I53" s="4" t="n"/>
-      <c r="J53" s="4" t="n"/>
-      <c r="K53" s="4" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="18" t="inlineStr">
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
+      <c r="F54" s="4" t="n"/>
+      <c r="G54" s="4" t="n"/>
+      <c r="H54" s="4" t="n"/>
+      <c r="I54" s="4" t="n"/>
+      <c r="J54" s="4" t="n"/>
+      <c r="K54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
@@ -2158,21 +2202,21 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A51:K51"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A54:K54"/>
     <mergeCell ref="A41:E41"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="G18:K18"/>
     <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A55:K55"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A17:K17"/>
     <mergeCell ref="G4:K4"/>
-    <mergeCell ref="A53:K53"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A29:K29"/>
     <mergeCell ref="G32:K32"/>
+    <mergeCell ref="A52:K52"/>
     <mergeCell ref="G41:K41"/>
     <mergeCell ref="A28:K28"/>
     <mergeCell ref="A40:K40"/>

--- a/reports/pdf_rolling5_20261006.xlsx
+++ b/reports/pdf_rolling5_20261006.xlsx
@@ -1364,23 +1364,23 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>녹십자</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>657934201</v>
+        <v>954998292</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>3.57%→3.68%</t>
+          <t>8.24%→8.41%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>178→188</t>
+          <t>286→296</t>
         </is>
       </c>
       <c r="G25" s="17" t="n"/>
@@ -1392,23 +1392,23 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>녹십자</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>954998292</v>
+        <v>657934201</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>8.24%→8.41%</t>
+          <t>3.57%→3.68%</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>286→296</t>
+          <t>178→188</t>
         </is>
       </c>
       <c r="G26" s="17" t="n"/>
@@ -1737,7 +1737,7 @@
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 316억   ·   현금 4억(1.2%)      오늘 2026-10-06  vs  5일전 2026-09-28      매수 7종목  /  매도 8종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 316억   ·   현금 2억(0.6%)      오늘 2026-10-06  vs  5일전 2026-09-28      매수 7종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B40" s="4" t="n"/>

--- a/reports/pdf_rolling5_20261006.xlsx
+++ b/reports/pdf_rolling5_20261006.xlsx
@@ -1364,23 +1364,23 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>녹십자</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>954998292</v>
+        <v>657934201</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>8.24%→8.41%</t>
+          <t>3.57%→3.68%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>286→296</t>
+          <t>178→188</t>
         </is>
       </c>
       <c r="G25" s="17" t="n"/>
@@ -1392,23 +1392,23 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>녹십자</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>657934201</v>
+        <v>954998292</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>3.57%→3.68%</t>
+          <t>8.24%→8.41%</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>178→188</t>
+          <t>286→296</t>
         </is>
       </c>
       <c r="G26" s="17" t="n"/>
@@ -2002,23 +2002,23 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>57391983</v>
+        <v>80375976</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>2.17%→2.35%</t>
+          <t>3.81%→4.08%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>238→258</t>
+          <t>299→319</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
@@ -2046,23 +2046,23 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>80375976</v>
+        <v>57391983</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>3.81%→4.08%</t>
+          <t>2.17%→2.35%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>299→319</t>
+          <t>238→258</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
